--- a/medical_surveys_questionnaires/044_global_health_literacy_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/044_global_health_literacy_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'55_or_above'}</t>
+          <t>55_or_above</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '55 or above'}</t>
+          <t>55 or above</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'very_low'}</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'very_good'}</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'extremely_good'}</t>
+          <t>extremely_good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'extremely_good'}</t>
+          <t>extremely good</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_have_a_good_understanding'}</t>
+          <t>i_have_a_good_understanding</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I have a good understanding'}</t>
+          <t>I have a good understanding</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_have_some_understanding'}</t>
+          <t>i_have_some_understanding</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I have some understanding'}</t>
+          <t>I have some understanding</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'i_have_very_little_understanding'}</t>
+          <t>i_have_very_little_understanding</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'I have very little understanding'}</t>
+          <t>I have very little understanding</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'i_do_not_understand'}</t>
+          <t>i_do_not_understand</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'I do not understand'}</t>
+          <t>I do not understand</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_high_risk'}</t>
+          <t>very_high_risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'very_high_risk'}</t>
+          <t>very high risk</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'very_low'}</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'not_applicable'}</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'0-25'}</t>
+          <t>0-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '0-25'}</t>
+          <t>0-25</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'26-50'}</t>
+          <t>26-50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '26-50'}</t>
+          <t>26-50</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'51-75'}</t>
+          <t>51-75</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '51-75'}</t>
+          <t>51-75</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'76-100'}</t>
+          <t>76-100</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '76-100'}</t>
+          <t>76-100</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_easy'}</t>
+          <t>very_easy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'very_easy'}</t>
+          <t>very easy</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'difficult'}</t>
+          <t>difficult</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'difficult'}</t>
+          <t>difficult</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_difficult'}</t>
+          <t>very_difficult</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'very_difficult'}</t>
+          <t>very difficult</t>
         </is>
       </c>
     </row>
